--- a/AAII_Financials/Quarterly/AVT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>AVT</t>
   </si>
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44198</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44107</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8295400</v>
+      </c>
+      <c r="E8" s="3">
         <v>7119800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6319000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5898600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5617800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5315400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5663400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5604200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5563000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5653600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6204900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6335600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6554600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6514600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6717500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6750100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6372700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6488100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5865200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5584700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5226700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4916700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4668200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4723100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17634300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13474600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4534800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4630000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4680900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4698800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5049000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5089900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5059200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4795100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4521600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4660900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4606400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4441900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4273600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4118100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7430300</v>
+      </c>
+      <c r="E9" s="3">
         <v>6380700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5655900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5283800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5024100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4727600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5067300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4996800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4920100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4984300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5498700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5587500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5736600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5702800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5933400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5982000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5593000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5675100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5152200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4925000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4581800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4348400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4156900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4207000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15570900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11886200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4009200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4086200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4085800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4074600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4418900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4453100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4400600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4141600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3919200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4048400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3975800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3811900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3687400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3595400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>865000</v>
+      </c>
+      <c r="E10" s="3">
         <v>739100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>663000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>614800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>593700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>587900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>596100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>607400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>642900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>669300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>706200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>748100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>818000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>811800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>784100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>768100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>779700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>813000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>713000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>659700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>644900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>568300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>511300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>516100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2063400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1588400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>525600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>543800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>595100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>624200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>630100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>636800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>658600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>653500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>602400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>612500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>630600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>630000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>586200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>522700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,8 +1244,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1353,8 +1367,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,175 +1492,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>86500</v>
+      </c>
+      <c r="E14" s="3">
         <v>14700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>25200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8300</v>
       </c>
-      <c r="G14" s="3">
-        <v>83600</v>
-      </c>
       <c r="H14" s="3">
+        <v>68700</v>
+      </c>
+      <c r="I14" s="3">
         <v>9100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>26400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>52600</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-83800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>42100</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-61700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>26300</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>5300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>28400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>17600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>11900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>41600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>226000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>219200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>14300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>24600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>165600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>62300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>14800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>36800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>206600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>36800</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>92800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>42000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>33500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>30400</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E15" s="3">
         <v>18800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>22600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>21300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1683,8 +1706,8 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
@@ -1701,26 +1724,29 @@
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL15" s="3">
         <v>11900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>23200</v>
       </c>
-      <c r="AM15" s="3" t="s">
+      <c r="AN15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>20400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>7900</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7975900</v>
+      </c>
+      <c r="E17" s="3">
         <v>6897600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6145600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5746300</v>
       </c>
-      <c r="G17" s="3">
-        <v>5457900</v>
-      </c>
       <c r="H17" s="3">
+        <v>5472700</v>
+      </c>
+      <c r="I17" s="3">
         <v>5160100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5501300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5432600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5342400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5459700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5959600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6075400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6286000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6196100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6356800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6459600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6088000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6213700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5653500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5416500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5108700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4829000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4611000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4719800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17639000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13481200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4488300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4567300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4710900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4545700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4952900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4943100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4937700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4849500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4434600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4596400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4513000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4325600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4149300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3988600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>319500</v>
+      </c>
+      <c r="E18" s="3">
         <v>222200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>173400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>152300</v>
       </c>
-      <c r="G18" s="3">
-        <v>159900</v>
-      </c>
       <c r="H18" s="3">
+        <v>145100</v>
+      </c>
+      <c r="I18" s="3">
         <v>155300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>162100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>171600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>220600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>193900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>245300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>260300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>268600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>318500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>360700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>290500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>284700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>274400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>211700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>168200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>118000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>87700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>57200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>46500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>62700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>153100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>96100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>146800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>121500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-54400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>87000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>64500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>93400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>116300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>124300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>129500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,618 +2081,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6900</v>
       </c>
-      <c r="G20" s="3">
-        <v>13800</v>
-      </c>
       <c r="H20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="I20" s="3">
         <v>5600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>17400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-39400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>8800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>8400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>19000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-13500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>17400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-36600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>336400</v>
+      </c>
+      <c r="E21" s="3">
         <v>237900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>195500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>162200</v>
       </c>
-      <c r="G21" s="3">
-        <v>164400</v>
-      </c>
       <c r="H21" s="3">
+        <v>153700</v>
+      </c>
+      <c r="I21" s="3">
         <v>166100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>174800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>186200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>237400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>198000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>255500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>285000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>331600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>336100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>383500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>313300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>303100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>298900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>239200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>194900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>143800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>121200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>88400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>41000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>175400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>121600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>92500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>112200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>16800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>208300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>141800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>191100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>168900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>13200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>148800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>147300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>137300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>174300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>123500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>137400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E22" s="3">
         <v>63900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>61800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>60300</v>
       </c>
-      <c r="G22" s="3">
-        <v>55100</v>
-      </c>
       <c r="H22" s="3">
+        <v>59200</v>
+      </c>
+      <c r="I22" s="3">
         <v>62400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>63700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>65100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>60900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>74600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>75500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>71800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>75600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>71200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>59000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>45100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>30000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>25900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>22300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>22300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>122700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>97300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>33900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>33600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>34800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>36300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>33700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>30100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>26000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>25600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>22000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>25200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>27500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>26700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E23" s="3">
         <v>140600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>89900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>76800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>78100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>90300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>74700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>101300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>101900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>153600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>275400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>190400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>243600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>303100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>245800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>248500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>248000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>191800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>145000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>91700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>70100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>34400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-23300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-129600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-113400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>34000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-63000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>125600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>64900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>114800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>93500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-72100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>62100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>61500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>54700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>106200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>61000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>88500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E24" s="3">
         <v>46200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-9800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>18700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>66200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>56200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>59200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>61500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>64600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>41000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>33700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>15200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-98500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-30200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-27900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>30600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>39700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>243500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-18600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>16300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>28500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>20900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E26" s="3">
         <v>94300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>61700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>87900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>87300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>59000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>82700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>88800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>117900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>209300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>155300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>187400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>243900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>184300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>246800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>183400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>150800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>111300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>85400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>107500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>41800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-35100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>94900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>56000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>75100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-315600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>67900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>58200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>73300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>89900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>32500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>67700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E27" s="3">
         <v>94300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>61700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>87900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>87300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>59000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>88800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>117900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>209300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>155300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>187400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>243900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>184300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>246800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>183400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>150800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>85400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>107500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>41800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-35100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>94900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>56000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>75100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-315600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>67900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>58200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>73300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>89900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>32500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>67700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3269,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -3220,56 +3281,59 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>3300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-19600</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>8600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>46100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-21200</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>100</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>8200</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>181900</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>70800</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-13800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-5600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-17400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>39400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>9600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-8400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>13500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-17400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>36600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E33" s="3">
         <v>94300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>61700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>87900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>87300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>59000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>88800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>117900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>209300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>155300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>187400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>243900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>184300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>246800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>183400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>150800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>111300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>85400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>107500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>41800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-31800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>88000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>36400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>83700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-320100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>46700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>58300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>81400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>271800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>103200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E35" s="3">
         <v>94300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>61700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>87900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>87300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>59000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>88800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>117900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>209300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>155300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>187400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>243900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>184300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>246800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>183400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>150800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>111300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>85400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>107500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>41800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-31800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>88000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>36400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>83700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-320100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>46700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>58300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>81400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>271800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>103200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44198</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44107</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,130 +4301,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E41" s="3">
         <v>202400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>286500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>175500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>192400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>188900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>172100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>267500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>310900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>218500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>272900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>278700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>288200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>185900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>324800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>80900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>153700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>199500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>167800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>299100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>199700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>322700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>376300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>483100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>477000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>402700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>488800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>664100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>546100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>725300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>482200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>365900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>621100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>430100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>589500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>539700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>836400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1129200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1270100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1196500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4435,525 +4525,540 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-      <c r="AI42" s="3" t="s">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>75100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>136400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>197900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>281300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>261500</v>
-      </c>
-      <c r="AO42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AP42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6883000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5502300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5242800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4503500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4327500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4095500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4421400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4575900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4391200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4315100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4508700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4679700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4763800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4670600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4789400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4591000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4301000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4164600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4077700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3720300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3576100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3365700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3105300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2964500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2928400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2987800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2977800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3129400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3168400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3188900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3445800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3682500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3641100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3552500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3295000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3417400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3337600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3237400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2996100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2876300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6069400</v>
+      </c>
+      <c r="E44" s="3">
         <v>5462400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5294500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5420900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5235500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5270500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5252500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5614100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5468700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5751900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6116000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5755100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5465000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5354000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4972900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4655000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4244100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3680800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3542700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3283800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3236800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2760200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2816400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2944700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2732000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2745200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2908600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3026000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3008400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3212000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3306300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3395200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3141800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3261900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3285900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3129000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2824700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2771200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2697800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2418800</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E45" s="3">
         <v>8800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>43800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>69100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>50600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>216500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>183000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>177800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>172800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>156000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>161800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>150800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>156000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>156400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>209900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>191400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>181000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>161300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>169500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>153400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>129300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>156500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>114400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>206500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>305100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>269200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>261600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>253800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>273500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>4113100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>3208100</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13333800</v>
+      </c>
+      <c r="E46" s="3">
         <v>11384800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11024200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10327000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10018700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9795400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10072400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10679200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10370600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10485800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11139000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10911100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10750900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10443500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10303600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9509900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8876600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8217600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7944200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7465100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7163400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6604600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6454400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6602200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6328800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6316600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6536500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6988900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6876300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7255400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7390700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7558000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7610600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7624600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7576100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>7545700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>7533800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>7673000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>11077100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>9699800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>25900</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -4961,8 +5066,8 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>23500</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -4991,8 +5096,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5069,252 +5174,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>893500</v>
+      </c>
+      <c r="E48" s="3">
         <v>867900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>879300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>866600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>869100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>758000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>767000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>795900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>777100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>781100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>790900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>691600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>663300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>623200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>607800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>527000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>542300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>568600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>586200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>609500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>634400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>656700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>688200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>692800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>680500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>684600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>705800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>716000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>452200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>455500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>462900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>525900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>522900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>520900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>507700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>510300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>519600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>526000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>565100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>471300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>810200</v>
+      </c>
+      <c r="E49" s="3">
         <v>817000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>826500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>818100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>837000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>795100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>773700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>818900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>781000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>780500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>787000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>759800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>780600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>770900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>755000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>703800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>771500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>821400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>843000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>847000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>866600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>872200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>873600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>846300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>839200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>838200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1035200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>978800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1020200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1195800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1195500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1181700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1200800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1284800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1450800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1469000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1425600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1426400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1394500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>641700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E52" s="3">
         <v>419600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>423200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>402700</v>
       </c>
-      <c r="G52" s="3">
-        <v>46100</v>
-      </c>
       <c r="H52" s="3">
+        <v>69600</v>
+      </c>
+      <c r="I52" s="3">
         <v>363900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>330000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>303600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>77300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>277800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>280300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>283800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>95200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>271700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>263500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>227600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>198100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>174100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>207400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>289700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>260900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>232300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>248100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>240100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>256700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>250200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>247600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>229600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>215800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>193000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>185500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>188200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>262600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>281600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>266000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>248200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>220600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>220400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>219300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>233400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15425400</v>
+      </c>
+      <c r="E54" s="3">
         <v>13489300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13153200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12414400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12118600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11712300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11942900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12597600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12209100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12325200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12997200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12646500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12477200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12109300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11929900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10968400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10388500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9781700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9580900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9211300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8925400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8365900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8264300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8381400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8105200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8089700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8525100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8913300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8564600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9099700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9234700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9453800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9596800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9711900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9800500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9773200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9699600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9845800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>13256000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>11046100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6054300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4625900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4343400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3688900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3487400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3319000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3626300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3588000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3345500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3324000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3308100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3445700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3373800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3136900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3106700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3466600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3431700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2968800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2693700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2467700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2401400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2001700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1935700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2005100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1754100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1733700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1802500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2025500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1864300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1836500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2046600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2352800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2269500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2091100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1958100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1917700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1861600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1731300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1774000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1463600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>789800</v>
+      </c>
+      <c r="E58" s="3">
         <v>520900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>516300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>244100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>143500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>56100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>579600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>546700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>603600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>751800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>122300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>122400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>128200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>209400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>513000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>174400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>424200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>350000</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>23100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>300000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>311800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>167000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>400000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>492200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>638400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>300500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>50400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>10600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>165400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>102000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>243400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>195500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>50100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>32600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>246700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>323700</v>
+      </c>
+      <c r="E59" s="3">
         <v>17000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>182500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>275300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>29300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>82100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>60600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>341400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>45500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>741600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>679600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>645500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>672800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>644800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>645600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>630800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>584200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>578900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>594300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>526200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>474200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>450500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>473400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>413700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>446300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>424400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>501400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>534600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>576400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>554100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>598500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>542000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>880800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2789000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1872300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7503400</v>
+      </c>
+      <c r="E60" s="3">
         <v>5663400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5334000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4373900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4128100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4014400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4206100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4747900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4465300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4492700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4765600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4290400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4249400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3969800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4057700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4659200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4251700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4065800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3688500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3113300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3055200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2885900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2826300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2766400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2280400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2607800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2745300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3137300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2578600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2333300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2472800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2864800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2969500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2769400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2755600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2711700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2453800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2644600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4809800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>3433900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2686000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2651600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2651000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2954900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2734200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2632200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2733200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2606100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2580500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2589800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2945000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3288600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3178700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3225400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2979800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1825500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1437400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>922000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1144600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1389700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1191300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>895900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>895600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1195200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1424800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1194200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1194100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1192000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1419900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2023600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1961500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1554700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1489200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1488700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1488100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1495100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1729200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1724200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3382400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2609600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>213500</v>
+      </c>
+      <c r="E62" s="3">
         <v>220900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>230300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>237400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>244800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>180800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>159800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>205900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>237900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>253600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>276200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>244900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>297500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>278600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>462700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>464400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>506700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>537100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>544500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>562700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>594700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>646200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>631600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>642300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>673600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>610400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>628400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>626000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>425600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>380300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>391700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>413100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>453100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>499000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>308300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>322200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>334500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>377300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>351900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10402900</v>
+      </c>
+      <c r="E66" s="3">
         <v>8536000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8215200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7566300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7107100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6827400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7099000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7559800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7283600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7336100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7986800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7823900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7725500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7473700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7500200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6949100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6195800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5525000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5377600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5065700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4841200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4428000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4353600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4603900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4378800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4412500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4567800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4955300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4424100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4737200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4826000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4832700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4911800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4757100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4552000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4529100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4517500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4746200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8544100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6257100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3513200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3415300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3349700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3316400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3430200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3501200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3541800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3533900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3601800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3625000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3564200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3532700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3378200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3249900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3089000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2934200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2921400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2799800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2686000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2593400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2516200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2452700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2366100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2367700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2421800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2390400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2575500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2678300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2767500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2935100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2982900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3139300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3235900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3313900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3725000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3765500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3799400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3872400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3760900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3679400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5022500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4953300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4937900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4848100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5011500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4885000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4843900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5037700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4925500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4989100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5010400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4822600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4751700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4635600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4429700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4019300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4192800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4256700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4203200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4145600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4084200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3937900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3910700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3777500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3726400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3677300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3957300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3958100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4140500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4362500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4408700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4621100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4685100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4954800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5248500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5244100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5182100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5099600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4711900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4789000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44198</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44107</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E81" s="3">
         <v>94300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>61700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>87900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>87300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>59000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>88800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>117900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>209300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>155300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>187400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>243900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>184300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>246800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>183400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>150800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>111300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>85400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>107500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>41800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-31800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>88000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>36400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>83700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-320100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>46700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>58300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>81400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>271800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>103200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E83" s="3">
         <v>28600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>35400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>33000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>21300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>28700</v>
       </c>
       <c r="X83" s="3">
         <v>28700</v>
       </c>
       <c r="Y83" s="3">
+        <v>28700</v>
+      </c>
+      <c r="Z83" s="3">
         <v>32500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>42000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>182200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>137800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>46500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>44600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>45000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>46500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>46200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>50900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>59200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>61000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>63800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>57400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>40600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>35800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-290700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-53800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>208200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-144600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>139500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>140900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>337800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>106300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>274300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>499300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-42300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-41300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>234500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-321400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-645100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-199900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>243800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-232200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-31000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-106600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>85000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>122400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>730200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>442600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>148600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>195600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>334600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>269200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>15900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-85000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>235600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>77100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>68800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-128000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-184100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-424700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>240200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-31800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-82000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-76100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-56900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-83200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-12000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-73500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-14400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-21300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-41000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-43700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-44800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-40700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-26700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-37500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-35700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-34700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-59600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-41900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-81900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-75800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-106800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>57900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-37900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-125200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-66500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-42400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-22900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>6000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-87300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>79100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>41600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>27700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>5300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>2208800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-829700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-34400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,8 +10451,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10227,121 +10461,124 @@
         <v>28700</v>
       </c>
       <c r="E96" s="3">
-        <v>28500</v>
+        <v>28700</v>
       </c>
       <c r="F96" s="3">
         <v>28500</v>
       </c>
       <c r="G96" s="3">
+        <v>28500</v>
+      </c>
+      <c r="H96" s="3">
         <v>27700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>28200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>28600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>28900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>27800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>28000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>27800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>28300</v>
-      </c>
-      <c r="O96" s="3">
-        <v>26500</v>
       </c>
       <c r="P96" s="3">
         <v>26500</v>
       </c>
       <c r="Q96" s="3">
+        <v>26500</v>
+      </c>
+      <c r="R96" s="3">
         <v>-26300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-27000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-25200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-25600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-23700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-23900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-21900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-20900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-20800</v>
       </c>
       <c r="Z96" s="3">
         <v>-20800</v>
       </c>
       <c r="AA96" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-63200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-21500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-21500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-21800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-22900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-22100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-22600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-21600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-22000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-22200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-23100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-21800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-21700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>257700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-84000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>155100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-79800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-403400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-109400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-149300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-507100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>122400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-67700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-134100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>668100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>588400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>159700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-202900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>56800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>142500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-184600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-88300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-644600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-444400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-261300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-494200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-29500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>187300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-246200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-72200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-240100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-49500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-180100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-140900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>695900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>193800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-14500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-13700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>9800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-12500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-13900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>6100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>38300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>11900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-32800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-84100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>111100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-95400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-43400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>92500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-54400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>102300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-138800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>243900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-72800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-45800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>31600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-131300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>99400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-123100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-106700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-69100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-143500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-175300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>118000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-179100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>243100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>116300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-255300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>191100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-159500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>49800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-296700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-292800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-140900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>73600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>165100</v>
       </c>
     </row>
